--- a/outputs/Block5B_Senate_Specification_Contract.xlsx
+++ b/outputs/Block5B_Senate_Specification_Contract.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Candidate</t>
   </si>
@@ -37,43 +37,25 @@
     <t>PooledPollStructure</t>
   </si>
   <si>
-    <t>PooledPopularContext</t>
-  </si>
-  <si>
-    <t>PooledNationalReduced</t>
-  </si>
-  <si>
     <t>PooledFullV11</t>
   </si>
   <si>
     <t>PartialPoolFull</t>
   </si>
   <si>
-    <t>Poll structure and incumbency only</t>
-  </si>
-  <si>
-    <t>Adds frozen national popular-vote context</t>
-  </si>
-  <si>
-    <t>Adds non-quota national Senate context</t>
-  </si>
-  <si>
-    <t>Exact pooled production specification inherited from v12</t>
-  </si>
-  <si>
-    <t>Regularized state effects; safer alternative to 11 tiny models</t>
+    <t>Race-level poll structure and incumbent party only</t>
+  </si>
+  <si>
+    <t>Production pooled state-error model: race-level poll structure + frozen national popular-vote context; no legacy bucket signals</t>
+  </si>
+  <si>
+    <t>Clean-feature challenger with regularized state effects</t>
   </si>
   <si>
     <t>Expected Margin 2P, Abs Poll Margin 2P, Unallocated Poll Share, Incumbent D Indicator</t>
   </si>
   <si>
     <t>Expected Margin 2P, Abs Poll Margin 2P, Unallocated Poll Share, Incumbent D Indicator, National Vote Margin 2P</t>
-  </si>
-  <si>
-    <t>Expected Margin 2P, Abs Poll Margin 2P, Unallocated Poll Share, Incumbent D Indicator, National Vote Margin 2P, National Senate Net Gain Signal, National Senate Flip Pressure, Incumbent Vulnerability Signal</t>
-  </si>
-  <si>
-    <t>Expected Margin 2P, Abs Poll Margin 2P, Unallocated Poll Share, National Vote Margin 2P, D-Held Loss Pressure, R-Held Loss Pressure, National Senate Net Gain Signal, National Senate Flip Pressure, Incumbent Vulnerability Signal</t>
   </si>
   <si>
     <t>None</t>
@@ -437,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -465,13 +447,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -485,13 +467,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -505,58 +487,18 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
